--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-04-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-04-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שיראל חדד - תרבחו ותסעדו</v>
+        <v>סנדי דינקל - קברי הצדיקים - גרסה ווקאלית</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-11</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410424&amp;sid=35b0c9b5d56599de903ce4d9ab0f610f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410441&amp;sid=0afa63215d0cbd102cc48a858ac6b064</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שיראל חדד - תרבחו ותסעדו</v>
+        <v>סנדי דינקל - קברי הצדיקים - גרסה ווקאלית</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>שיראל חדד - הבטחת לי עולם</v>
+        <v>פבלו רוזנברג - Quiero Volver</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-11</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410423&amp;sid=35b0c9b5d56599de903ce4d9ab0f610f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410440&amp;sid=0afa63215d0cbd102cc48a858ac6b064</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>שיראל חדד - הבטחת לי עולם</v>
+        <v>פבלו רוזנברג - Quiero Volver</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>שיראל חדד - אתה לא מבין</v>
+        <v>שחר חדד - כמעט כרעתי ברך</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-11</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410422&amp;sid=35b0c9b5d56599de903ce4d9ab0f610f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410438&amp;sid=0afa63215d0cbd102cc48a858ac6b064</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>שיראל חדד - אתה לא מבין</v>
+        <v>שחר חדד - כמעט כרעתי ברך</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>שימי תבורי - עד מתי</v>
+        <v>עוז תירם - אני שלך</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-11</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410421&amp;sid=35b0c9b5d56599de903ce4d9ab0f610f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410437&amp;sid=0afa63215d0cbd102cc48a858ac6b064</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>שימי תבורי - עד מתי</v>
+        <v>עוז תירם - אני שלך</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>עמית שרעבי - הסטייל הישראלי</v>
+        <v>נועה קירל - מצאתי פינה</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-11</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410420&amp;sid=35b0c9b5d56599de903ce4d9ab0f610f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410436&amp;sid=0afa63215d0cbd102cc48a858ac6b064</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>עמית שרעבי - הסטייל הישראלי</v>
+        <v>נועה קירל - מצאתי פינה</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>נתי גדמו - זה אני</v>
+        <v>זכי צברי - החגיגה</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-11</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410419&amp;sid=35b0c9b5d56599de903ce4d9ab0f610f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410435&amp;sid=0afa63215d0cbd102cc48a858ac6b064</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -659,21 +659,21 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>נתי גדמו - זה אני</v>
+        <v>זכי צברי - החגיגה</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>נטע ברזילי - לבד לבד לבד</v>
+        <v>אלי אליאב - מחרוזת חלומות 2026</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-11</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410418&amp;sid=35b0c9b5d56599de903ce4d9ab0f610f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410434&amp;sid=0afa63215d0cbd102cc48a858ac6b064</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -697,21 +697,21 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>נטע ברזילי - לבד לבד לבד</v>
+        <v>אלי אליאב - מחרוזת חלומות 2026</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>נועם דדון - מחרוזת נכון להיום 2026</v>
+        <v>אבישי עוזיאל - משהו נפתח - משהו נשרף</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-11</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410417&amp;sid=35b0c9b5d56599de903ce4d9ab0f610f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410432&amp;sid=0afa63215d0cbd102cc48a858ac6b064</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -735,202 +735,12 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>נועם דדון - מחרוזת נכון להיום 2026</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>מקסים משעלי - משא וראח</v>
-      </c>
-      <c r="B10" t="str">
-        <v>2026-04-09</v>
-      </c>
-      <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410416&amp;sid=35b0c9b5d56599de903ce4d9ab0f610f</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-04-09</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v>מקסים משעלי - משא וראח</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>מיכאל סבאג - אתה עוד יכול</v>
-      </c>
-      <c r="B11" t="str">
-        <v>2026-04-09</v>
-      </c>
-      <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410415&amp;sid=35b0c9b5d56599de903ce4d9ab0f610f</v>
-      </c>
-      <c r="D11" t="str">
-        <v>2026-04-09</v>
-      </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J11" t="str">
-        <v/>
-      </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
-      <c r="L11" t="str">
-        <v>מיכאל סבאג - אתה עוד יכול</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>אריה פרננד - הבוץ הלבנוני</v>
-      </c>
-      <c r="B12" t="str">
-        <v>2026-04-09</v>
-      </c>
-      <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410414&amp;sid=35b0c9b5d56599de903ce4d9ab0f610f</v>
-      </c>
-      <c r="D12" t="str">
-        <v>2026-04-09</v>
-      </c>
-      <c r="E12" t="str">
-        <v/>
-      </c>
-      <c r="F12" t="str">
-        <v/>
-      </c>
-      <c r="G12" t="str">
-        <v/>
-      </c>
-      <c r="H12" t="str">
-        <v/>
-      </c>
-      <c r="I12" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J12" t="str">
-        <v/>
-      </c>
-      <c r="K12" t="str">
-        <v/>
-      </c>
-      <c r="L12" t="str">
-        <v>אריה פרננד - הבוץ הלבנוני</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>אופק יצחקי - מחרוזת שחק אותה קוסם 2026</v>
-      </c>
-      <c r="B13" t="str">
-        <v>2026-04-09</v>
-      </c>
-      <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410413&amp;sid=35b0c9b5d56599de903ce4d9ab0f610f</v>
-      </c>
-      <c r="D13" t="str">
-        <v>2026-04-09</v>
-      </c>
-      <c r="E13" t="str">
-        <v/>
-      </c>
-      <c r="F13" t="str">
-        <v/>
-      </c>
-      <c r="G13" t="str">
-        <v/>
-      </c>
-      <c r="H13" t="str">
-        <v/>
-      </c>
-      <c r="I13" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J13" t="str">
-        <v/>
-      </c>
-      <c r="K13" t="str">
-        <v/>
-      </c>
-      <c r="L13" t="str">
-        <v>אופק יצחקי - מחרוזת שחק אותה קוסם 2026</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>אבשי - קוראים לי</v>
-      </c>
-      <c r="B14" t="str">
-        <v>2026-04-09</v>
-      </c>
-      <c r="C14" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410412&amp;sid=35b0c9b5d56599de903ce4d9ab0f610f</v>
-      </c>
-      <c r="D14" t="str">
-        <v>2026-04-09</v>
-      </c>
-      <c r="E14" t="str">
-        <v/>
-      </c>
-      <c r="F14" t="str">
-        <v/>
-      </c>
-      <c r="G14" t="str">
-        <v/>
-      </c>
-      <c r="H14" t="str">
-        <v/>
-      </c>
-      <c r="I14" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J14" t="str">
-        <v/>
-      </c>
-      <c r="K14" t="str">
-        <v/>
-      </c>
-      <c r="L14" t="str">
-        <v>אבשי - קוראים לי</v>
+        <v>אבישי עוזיאל - משהו נפתח - משהו נשרף</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-04-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-04-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>סנדי דינקל - קברי הצדיקים - גרסה ווקאלית</v>
+        <v>רגב קהלני - סיבה לאהבה</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410441&amp;sid=0afa63215d0cbd102cc48a858ac6b064</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410452&amp;sid=31ee18b6f0ccb07be0d6a8d384e92647</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>סנדי דינקל - קברי הצדיקים - גרסה ווקאלית</v>
+        <v>רגב קהלני - סיבה לאהבה</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>פבלו רוזנברג - Quiero Volver</v>
+        <v>רביב כנר - כיסופים</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410440&amp;sid=0afa63215d0cbd102cc48a858ac6b064</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410451&amp;sid=31ee18b6f0ccb07be0d6a8d384e92647</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>פבלו רוזנברג - Quiero Volver</v>
+        <v>רביב כנר - כיסופים</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>שחר חדד - כמעט כרעתי ברך</v>
+        <v>קובי גואני - הכי טוב בעולם</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410438&amp;sid=0afa63215d0cbd102cc48a858ac6b064</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410450&amp;sid=31ee18b6f0ccb07be0d6a8d384e92647</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>שחר חדד - כמעט כרעתי ברך</v>
+        <v>קובי גואני - הכי טוב בעולם</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>עוז תירם - אני שלך</v>
+        <v>דיויד טויב &amp; רפאל מדמון - עושה השלום - גרסה ווקאלית</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410437&amp;sid=0afa63215d0cbd102cc48a858ac6b064</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410449&amp;sid=31ee18b6f0ccb07be0d6a8d384e92647</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>עוז תירם - אני שלך</v>
+        <v>דיויד טויב &amp; רפאל מדמון - עושה השלום - גרסה ווקאלית</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>נועה קירל - מצאתי פינה</v>
+        <v>עילאי גניש - אל תגידי</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410436&amp;sid=0afa63215d0cbd102cc48a858ac6b064</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410448&amp;sid=31ee18b6f0ccb07be0d6a8d384e92647</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>נועה קירל - מצאתי פינה</v>
+        <v>עילאי גניש - אל תגידי</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>זכי צברי - החגיגה</v>
+        <v>עדן כהן - גבגבר</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410435&amp;sid=0afa63215d0cbd102cc48a858ac6b064</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410447&amp;sid=31ee18b6f0ccb07be0d6a8d384e92647</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -659,21 +659,21 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>זכי צברי - החגיגה</v>
+        <v>עדן כהן - גבגבר</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>אלי אליאב - מחרוזת חלומות 2026</v>
+        <v>נועה כהן - מחרוזת זוהר אשירוב 2 2026</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410434&amp;sid=0afa63215d0cbd102cc48a858ac6b064</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410446&amp;sid=31ee18b6f0ccb07be0d6a8d384e92647</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -697,21 +697,21 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>אלי אליאב - מחרוזת חלומות 2026</v>
+        <v>נועה כהן - מחרוזת זוהר אשירוב 2 2026</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>אבישי עוזיאל - משהו נפתח - משהו נשרף</v>
+        <v>מוריה כהן - געגוע</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410432&amp;sid=0afa63215d0cbd102cc48a858ac6b064</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410445&amp;sid=31ee18b6f0ccb07be0d6a8d384e92647</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -735,12 +735,88 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>אבישי עוזיאל - משהו נפתח - משהו נשרף</v>
+        <v>מוריה כהן - געגוע</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>ירדן טרופר - בית קברות לפרפרים</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-04-12</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410444&amp;sid=31ee18b6f0ccb07be0d6a8d384e92647</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-04-12</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>ירדן טרופר - בית קברות לפרפרים</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>אביב טל &amp; שובל - געגועים של אבא ובן</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-04-12</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410443&amp;sid=31ee18b6f0ccb07be0d6a8d384e92647</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-04-12</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>אביב טל &amp; שובל - געגועים של אבא ובן</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-04-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-04-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L14"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>רגב קהלני - סיבה לאהבה</v>
+        <v>אור חרזי - הנני</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-14</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410452&amp;sid=31ee18b6f0ccb07be0d6a8d384e92647</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410476&amp;sid=d20707e3871c5f5c479684e03c6d35cf</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>רגב קהלני - סיבה לאהבה</v>
+        <v>אור חרזי - הנני</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>רביב כנר - כיסופים</v>
+        <v>שיראל חדד - תפילה מהלב</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-14</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410451&amp;sid=31ee18b6f0ccb07be0d6a8d384e92647</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410475&amp;sid=d20707e3871c5f5c479684e03c6d35cf</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>רביב כנר - כיסופים</v>
+        <v>שיראל חדד - תפילה מהלב</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>קובי גואני - הכי טוב בעולם</v>
+        <v>עמיר בניון &amp; להקת הנוירונים - מי גילה לך את הסוד</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-14</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410450&amp;sid=31ee18b6f0ccb07be0d6a8d384e92647</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410474&amp;sid=d20707e3871c5f5c479684e03c6d35cf</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>קובי גואני - הכי טוב בעולם</v>
+        <v>עמיר בניון &amp; להקת הנוירונים - מי גילה לך את הסוד</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>דיויד טויב &amp; רפאל מדמון - עושה השלום - גרסה ווקאלית</v>
+        <v>סנדי דינקל - מי שאתה - גרסה ווקאלית</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-14</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410449&amp;sid=31ee18b6f0ccb07be0d6a8d384e92647</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410473&amp;sid=d20707e3871c5f5c479684e03c6d35cf</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>דיויד טויב &amp; רפאל מדמון - עושה השלום - גרסה ווקאלית</v>
+        <v>סנדי דינקל - מי שאתה - גרסה ווקאלית</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>עילאי גניש - אל תגידי</v>
+        <v>ניר קריגל - כטבמ</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-14</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410448&amp;sid=31ee18b6f0ccb07be0d6a8d384e92647</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410471&amp;sid=d20707e3871c5f5c479684e03c6d35cf</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>עילאי גניש - אל תגידי</v>
+        <v>ניר קריגל - כטבמ</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>עדן כהן - גבגבר</v>
+        <v>מיטל טרבלסי - יד מושטת</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-14</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410447&amp;sid=31ee18b6f0ccb07be0d6a8d384e92647</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410470&amp;sid=d20707e3871c5f5c479684e03c6d35cf</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -659,21 +659,21 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>עדן כהן - גבגבר</v>
+        <v>מיטל טרבלסי - יד מושטת</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>נועה כהן - מחרוזת זוהר אשירוב 2 2026</v>
+        <v>מורן מצליח - נופלת על היין</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-14</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410446&amp;sid=31ee18b6f0ccb07be0d6a8d384e92647</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410469&amp;sid=d20707e3871c5f5c479684e03c6d35cf</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -697,21 +697,21 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>נועה כהן - מחרוזת זוהר אשירוב 2 2026</v>
+        <v>מורן מצליח - נופלת על היין</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>מוריה כהן - געגוע</v>
+        <v>מאיר רובין &amp; ברק מזרחי - כואב לי שאתה בוכה אחי קאבר</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-14</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410445&amp;sid=31ee18b6f0ccb07be0d6a8d384e92647</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410468&amp;sid=d20707e3871c5f5c479684e03c6d35cf</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -735,21 +735,21 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>מוריה כהן - געגוע</v>
+        <v>מאיר רובין &amp; ברק מזרחי - כואב לי שאתה בוכה אחי קאבר</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>ירדן טרופר - בית קברות לפרפרים</v>
+        <v>ליאם יהודה - הכל שתיקות</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-14</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410444&amp;sid=31ee18b6f0ccb07be0d6a8d384e92647</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410467&amp;sid=d20707e3871c5f5c479684e03c6d35cf</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -773,21 +773,21 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>ירדן טרופר - בית קברות לפרפרים</v>
+        <v>ליאם יהודה - הכל שתיקות</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>אביב טל &amp; שובל - געגועים של אבא ובן</v>
+        <v>יאיר דוד - עלה - גרסת ווקאלית</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-14</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410443&amp;sid=31ee18b6f0ccb07be0d6a8d384e92647</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410466&amp;sid=d20707e3871c5f5c479684e03c6d35cf</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -811,12 +811,126 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>אביב טל &amp; שובל - געגועים של אבא ובן</v>
+        <v>יאיר דוד - עלה - גרסת ווקאלית</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>אליה והב &amp; יניב בן משיח - אבינו הגדול</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-04-14</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410465&amp;sid=d20707e3871c5f5c479684e03c6d35cf</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-04-14</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>אליה והב &amp; יניב בן משיח - אבינו הגדול</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>אלחנן ענבל - ממעמקים - גרסה ווקאלית</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-04-14</v>
+      </c>
+      <c r="C13" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410464&amp;sid=d20707e3871c5f5c479684e03c6d35cf</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-04-14</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>אלחנן ענבל - ממעמקים - גרסה ווקאלית</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>איציק דדיה - יצר טוב - גרסה ווקאלית</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-04-14</v>
+      </c>
+      <c r="C14" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410463&amp;sid=d20707e3871c5f5c479684e03c6d35cf</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2026-04-14</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v>איציק דדיה - יצר טוב - גרסה ווקאלית</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L14"/>
   </ignoredErrors>
 </worksheet>
 </file>